--- a/duoki_editor/resources/data/blank/海洋-一般疑问句_问句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-一般疑问句_问句认读-1-blank.xlsx
@@ -31,7 +31,7 @@
     <t>param1</t>
   </si>
   <si>
-    <t>海洋-一般疑问句_问句认读-1</t>
+    <t>服装店-一般疑问句_问句认读-1</t>
   </si>
   <si>
     <t>sentence_yes_no_question_demo</t>
@@ -82,22 +82,22 @@
     <t>npc2</t>
   </si>
   <si>
-    <t>哇！宝石精灵坐着彩虹飞来了！{npc2_name}，快来接受魔法挑战，赢取魔法宝石吧！第一个魔法问题来咯，{sentence_question_en}?</t>
-  </si>
-  <si>
-    <t>叮咚！答对啦！宝石精灵在为你欢呼哟！再来一个更有趣的魔法问题，它是飞鱼吗？Is it a flying fish？</t>
-  </si>
-  <si>
-    <t>{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>{sentence_answer_en_2}。</t>
-  </si>
-  <si>
-    <t>这一题也答对啦！{user_name}，{sentence_question_cn}?用英文怎么说呢?</t>
-  </si>
-  <si>
-    <t>哎呀，是调皮的风精灵偷走了你的声音吗？没关系，这句话用英文怎么说？{sentence_question_cn}?</t>
+    <t>哇！宝石精灵坐着彩虹飞来了！{npc2_name}，快来接受魔法挑战，赢取魔法宝石吧！第一个魔法问题来咯，{sentence_question_en}</t>
+  </si>
+  <si>
+    <t>答对啦！宝石精灵在为你欢呼哟！再来一个更有趣的魔法问题，它是飞鱼吗？Is it a flying fish？</t>
+  </si>
+  <si>
+    <t>{sentence_answer_en_1}</t>
+  </si>
+  <si>
+    <t>{sentence_answer_en_2}</t>
+  </si>
+  <si>
+    <t>这一题也答对啦！{user_name}，{sentence_question_cn} 用英文怎么说呢?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，是调皮的风精灵偷走了你的声音吗？没关系，这句话用英文怎么说？{sentence_question_cn} </t>
   </si>
   <si>
     <t>{sentence_question_en}</t>
@@ -106,13 +106,13 @@
     <t>我来帮你吧！ {sentence_question_en}</t>
   </si>
   <si>
-    <t>恭喜挑战成功！你们赢得了20颗宝石！</t>
-  </si>
-  <si>
-    <t>这次{npc2_name}帮了你，只能得到10颗宝石哦！下次要继续加油！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>恭喜挑战成功！你们赢得了10颗宝石！</t>
+  </si>
+  <si>
+    <t>这次{npc2_name}帮了你，只能得到5颗宝石哦！下次要继续加油！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
